--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486746_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486746_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.296799999999999</v>
+        <v>8.6882</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8031</v>
+        <v>6.7408</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4937</v>
+        <v>1.9474</v>
       </c>
       <c r="G2" t="n">
         <v>2.9187</v>
@@ -610,13 +610,13 @@
         <v>3.4754</v>
       </c>
       <c r="S2" t="n">
-        <v>0.436</v>
+        <v>0.8274</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6349</v>
+        <v>0.3028</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0709</v>
+        <v>0.5246</v>
       </c>
       <c r="V2" t="n">
         <v>3.3975</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5473</v>
+        <v>5.4853</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3028</v>
+        <v>4.9925</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2445</v>
+        <v>0.4928</v>
       </c>
       <c r="G3" t="n">
         <v>2.8537</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7169</v>
+        <v>0.6549</v>
       </c>
       <c r="T3" t="n">
-        <v>0.772</v>
+        <v>0.4617</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0551</v>
+        <v>0.1933</v>
       </c>
       <c r="V3" t="n">
         <v>2.1698</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6645</v>
+        <v>0.7657</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9550999999999999</v>
+        <v>-0.1612</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7094</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.2578</v>
+        <v>-2.4233</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.303</v>
+        <v>-0.7866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0452</v>
+        <v>-1.6366</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8984</v>
+        <v>-2.1599</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0612</v>
+        <v>-0.096</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1628</v>
+        <v>-2.0639</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3594</v>
+        <v>-0.2634</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2418</v>
+        <v>-0.6906</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1176</v>
+        <v>0.4272</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9308</v>
+        <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1234</v>
+        <v>0.131</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9854</v>
+        <v>-0.0625</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1381</v>
+        <v>0.1935</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7989</v>
+        <v>1.5133</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7989</v>
+        <v>3.0266</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3078</v>
+        <v>0.651</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6341</v>
+        <v>-0.1825</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6737</v>
+        <v>0.8336</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-2.2578</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4407</v>
+        <v>-2.303</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3639</v>
+        <v>0.0452</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0139</v>
+        <v>-0.8984</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0953</v>
+        <v>-1.0612</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>0.1628</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0629</v>
+        <v>-1.3594</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3454</v>
+        <v>-1.2418</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2826</v>
+        <v>-0.1176</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7707</v>
+        <v>1.11</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3511</v>
+        <v>0.8477</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4196</v>
+        <v>0.2622</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.7989</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>1.7989</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0699</v>
+        <v>0.1284</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2674</v>
+        <v>-0.6086</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1975</v>
+        <v>0.737</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1121</v>
+        <v>0.17</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7307</v>
+        <v>-0.4969</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6186</v>
+        <v>0.6669</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0267</v>
+        <v>0.5019</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6266</v>
+        <v>-0.1515</v>
       </c>
       <c r="L6" t="n">
         <v>0.6534</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1388</v>
+        <v>-0.3319</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1041</v>
+        <v>-0.3454</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9653</v>
+        <v>0.0135</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6673</v>
+        <v>-0.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3857</v>
+        <v>-0.1451</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2817</v>
+        <v>-0.0549</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1698</v>
+        <v>-0.6138</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4554</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2258</v>
+        <v>0.0818</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2023</v>
+        <v>-0.3932</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9765</v>
+        <v>0.475</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4233</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7866</v>
+        <v>-0.4407</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6366</v>
+        <v>0.3639</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1599</v>
+        <v>-0.0139</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.096</v>
+        <v>-0.0953</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0639</v>
+        <v>0.0814</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2634</v>
+        <v>-0.0629</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6906</v>
+        <v>-0.3454</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4272</v>
+        <v>0.2826</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.5446</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.51</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.8605</v>
+        <v>0.5448</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1036</v>
+        <v>0.3238</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2432</v>
+        <v>0.221</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.0266</v>
+        <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ SANCHEZ</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2621</v>
+        <v>-0.034</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0552</v>
+        <v>-0.157</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2069</v>
+        <v>0.123</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2069</v>
+        <v>-0.1121</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2069</v>
+        <v>-1.7307</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.6186</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.0267</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.6266</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6534</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2069</v>
+        <v>-0.1388</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2069</v>
+        <v>-1.1041</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.9653</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0552</v>
+        <v>0.7032</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0552</v>
+        <v>0.496</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.2072</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.1698</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>S. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7419</v>
+        <v>-0.2621</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1809</v>
+        <v>-0.0552</v>
       </c>
       <c r="F9" t="n">
-        <v>0.439</v>
+        <v>-0.2069</v>
       </c>
       <c r="G9" t="n">
-        <v>0.17</v>
+        <v>-0.2069</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4969</v>
+        <v>-0.2069</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6669</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5019</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1515</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6534</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3319</v>
+        <v>-0.2069</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3454</v>
+        <v>-0.2069</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0703</v>
+        <v>-0.0552</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7174</v>
+        <v>-0.0552</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3529</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6448</v>
+        <v>-2.1607</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9252</v>
+        <v>-0.615</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7196</v>
+        <v>-1.5458</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0222</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1326</v>
+        <v>0.3515</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0279</v>
+        <v>0.2824</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1047</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4554</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5629</v>
+        <v>-3.4829</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0551</v>
+        <v>-0.9999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5078</v>
+        <v>-2.483</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0483</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1104</v>
+        <v>-0.0552</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4554</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.357399999999998</v>
+        <v>8.909100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2643</v>
+        <v>7.815999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0931</v>
+        <v>1.093099999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-1.101400000000001</v>
@@ -1468,16 +1468,16 @@
         <v>17.377</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4467</v>
+        <v>3.9986</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7896</v>
+        <v>2.3412</v>
       </c>
       <c r="U13" t="n">
         <v>1.6574</v>
       </c>
       <c r="V13" t="n">
-        <v>1.185099999999999</v>
+        <v>1.1851</v>
       </c>
       <c r="W13" t="n">
         <v>13.705</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3942</v>
+        <v>3.7416</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0896</v>
+        <v>2.7101</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3046</v>
+        <v>1.0315</v>
       </c>
       <c r="G14" t="n">
         <v>-1.2127</v>
@@ -1546,13 +1546,13 @@
         <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0918</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1588</v>
+        <v>-0.5383</v>
       </c>
       <c r="U14" t="n">
-        <v>0.067</v>
+        <v>-0.2062</v>
       </c>
       <c r="V14" t="n">
         <v>7.2434</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1095</v>
+        <v>3.2337</v>
       </c>
       <c r="E15" t="n">
         <v>2.2675</v>
       </c>
       <c r="F15" t="n">
-        <v>0.842</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>2.6113</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9929</v>
+        <v>-0.8687</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6066</v>
+        <v>-0.4824</v>
       </c>
       <c r="V15" t="n">
         <v>1.1049</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7726</v>
+        <v>1.909</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4293</v>
+        <v>-0.119</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2019</v>
+        <v>2.0281</v>
       </c>
       <c r="G16" t="n">
         <v>2.0109</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6948</v>
+        <v>-0.5583</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7725</v>
+        <v>-0.4623</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.096</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1228</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2893</v>
+        <v>-0.0832</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1253</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4146</v>
+        <v>0.0421</v>
       </c>
       <c r="G17" t="n">
         <v>0.6465</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0278</v>
+        <v>-0.3447</v>
       </c>
       <c r="T17" t="n">
         <v>-0.5518</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5796</v>
+        <v>0.2072</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3505</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1414</v>
+        <v>-0.2518</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3758</v>
+        <v>0.1413</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.3931</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9046</v>
@@ -1858,13 +1858,13 @@
         <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6273</v>
+        <v>-0.7377</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8829</v>
+        <v>-0.3658</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7444</v>
+        <v>-0.3719</v>
       </c>
       <c r="V18" t="n">
         <v>1.3905</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1737</v>
+        <v>-0.9574</v>
       </c>
       <c r="E19" t="n">
-        <v>3.789</v>
+        <v>-0.5997</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.9628</v>
+        <v>-0.3577</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1237</v>
+        <v>1.9653</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2006</v>
+        <v>1.5516</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0769</v>
+        <v>0.4137</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2077</v>
+        <v>1.345</v>
       </c>
       <c r="K19" t="n">
-        <v>1.167</v>
+        <v>1.345</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.084</v>
+        <v>0.6203</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9664</v>
+        <v>0.2066</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1176</v>
+        <v>0.4137</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.5446</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.3862</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.1585</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.5446</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.3277</v>
+        <v>-0.193</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8404</v>
+        <v>-0.0139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5127</v>
+        <v>-0.1791</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.0113</v>
+        <v>-1.1851</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.9108</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1891</v>
+        <v>-3.0394</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8065</v>
+        <v>1.824</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3825</v>
+        <v>-4.8634</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9653</v>
+        <v>0.1237</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5516</v>
+        <v>0.2006</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4137</v>
+        <v>-0.0769</v>
       </c>
       <c r="J20" t="n">
-        <v>1.345</v>
+        <v>1.2077</v>
       </c>
       <c r="K20" t="n">
-        <v>1.345</v>
+        <v>1.167</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6203</v>
+        <v>-1.084</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2066</v>
+        <v>-0.9664</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4137</v>
+        <v>-0.1176</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3862</v>
+        <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4247</v>
+        <v>0.462</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2207</v>
+        <v>0.8754</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2039</v>
+        <v>-0.4133</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1851</v>
+        <v>-4.0113</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1851</v>
+        <v>-4.9108</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5518</v>
+        <v>-4.7587</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7442</v>
+        <v>-0.951</v>
       </c>
       <c r="F21" t="n">
         <v>-3.8077</v>
@@ -2092,10 +2092,10 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0827</v>
+        <v>-0.1241</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3032</v>
+        <v>0.0964</v>
       </c>
       <c r="U21" t="n">
         <v>-0.2205</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.867000000000001</v>
+        <v>-8.151199999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.7581</v>
+        <v>-6.241</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1089</v>
+        <v>-1.9102</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9598</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0537</v>
+        <v>-0.3379</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8277</v>
+        <v>-0.3106</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2259</v>
+        <v>-0.0273</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1851</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.357400000000002</v>
+        <v>-8.3574</v>
       </c>
       <c r="E23" t="n">
         <v>-1.093099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.2644</v>
+        <v>-7.264200000000001</v>
       </c>
       <c r="G23" t="n">
         <v>1.1014</v>
@@ -2248,16 +2248,16 @@
         <v>12.55</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.447</v>
+        <v>-3.4469</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6571</v>
+        <v>-1.6572</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.7896</v>
+        <v>-1.7895</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1852</v>
+        <v>-1.185200000000001</v>
       </c>
       <c r="W23" t="n">
         <v>12.5199</v>
